--- a/Adidas_failed_to_download.xlsx
+++ b/Adidas_failed_to_download.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A851"/>
+  <dimension ref="A1:A850"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -437,1702 +437,1702 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>15276153920</v>
+        <v>15278474295</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>15280224399</v>
+        <v>15281331903</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>15280112762</v>
+        <v>15280361201</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>15279751973</v>
+        <v>15278335488</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>15280406952</v>
+        <v>15278967938</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>15281028298</v>
+        <v>15279681274</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>15281318940</v>
+        <v>15277266398</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>15275945656</v>
+        <v>15277139592</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>15280975236</v>
+        <v>15281224320</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>15279707698</v>
+        <v>15279761132</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>15272184142</v>
+        <v>15281763779</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>15279193370</v>
+        <v>15280274289</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>15282430996</v>
+        <v>15282486382</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>15272767006</v>
+        <v>15276042545</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>15272184144</v>
+        <v>15279998524</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>15279744514</v>
+        <v>15274176863</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>15279356900</v>
+        <v>15278769409</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>15273277312</v>
+        <v>15281070924</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>15273738707</v>
+        <v>15282813092</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>15281165587</v>
+        <v>15276424033</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>15282278094</v>
+        <v>15265641778</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>15272765657</v>
+        <v>15279251126</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>15281235778</v>
+        <v>15282303227</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>15283230832</v>
+        <v>15279952250</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>15278144855</v>
+        <v>15279193370</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>15278474295</v>
+        <v>15280982536</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>15280906487</v>
+        <v>15280885745</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>15269968201</v>
+        <v>15270459133</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>15275810209</v>
+        <v>15280962783</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>586514541</v>
+        <v>15282409069</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>15280401699</v>
+        <v>15280601971</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>15278967933</v>
+        <v>15280239355</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>15270061416</v>
+        <v>15275370060</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>15281666025</v>
+        <v>15282327995</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>15283411918</v>
+        <v>15281020296</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>15277945199</v>
+        <v>15278144855</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>15279497173</v>
+        <v>15280980028</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>15281291696</v>
+        <v>15278898659</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>15279114294</v>
+        <v>15281411799</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>15281764706</v>
+        <v>15274471102</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>15268192994</v>
+        <v>15276907927</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>15268844193</v>
+        <v>15283334853</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>15270382927</v>
+        <v>15269859448</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>15275605076</v>
+        <v>15278431230</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>15276057417</v>
+        <v>15270024354</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>15279181235</v>
+        <v>15281230017</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>15278451924</v>
+        <v>15268558674</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>15279235255</v>
+        <v>15281214504</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>15270875337</v>
+        <v>15278699439</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>15281165693</v>
+        <v>15270737568</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>15277077778</v>
+        <v>15273872823</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>15272766488</v>
+        <v>15273488519</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>15282613812</v>
+        <v>15277709912</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>15281409700</v>
+        <v>15277057698</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>15283236753</v>
+        <v>15280769876</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>15280562891</v>
+        <v>15274547969</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>15282403666</v>
+        <v>15275544645</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>15275721392</v>
+        <v>15274984701</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>15273285991</v>
+        <v>15282202569</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>15278337540</v>
+        <v>15276246412</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>15276424037</v>
+        <v>15278358483</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>15279061619</v>
+        <v>15274984700</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>15280924850</v>
+        <v>15278434223</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>15274176863</v>
+        <v>15281409700</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>15274984700</v>
+        <v>15274823517</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>15275117568</v>
+        <v>15280372180</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>15279114785</v>
+        <v>15267898117</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>15278341034</v>
+        <v>15282384290</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>15277174179</v>
+        <v>15280355553</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>15273276079</v>
+        <v>15281531506</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>15276255517</v>
+        <v>15280123397</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>15270237795</v>
+        <v>15281988928</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>15268929026</v>
+        <v>15278774920</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>15276830486</v>
+        <v>15282735021</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>15281235151</v>
+        <v>15277945167</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>15281339674</v>
+        <v>15270812613</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>15275606635</v>
+        <v>15281818722</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>15283068940</v>
+        <v>15282733803</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>15277057698</v>
+        <v>15280726633</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>15281080714</v>
+        <v>15282293862</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>15279366507</v>
+        <v>15270464165</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>15270141908</v>
+        <v>15279254790</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>15278756166</v>
+        <v>15282296512</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>15281447643</v>
+        <v>15283100226</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>15282285273</v>
+        <v>15283096154</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>15273429555</v>
+        <v>15271468310</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>15279409656</v>
+        <v>15278474453</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>15282968321</v>
+        <v>15280453854</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>15283278326</v>
+        <v>15280691008</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>15278769866</v>
+        <v>15279249349</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>15269417011</v>
+        <v>15283043583</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>15283723505</v>
+        <v>15271938620</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>15278707472</v>
+        <v>15283166006</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>15277616885</v>
+        <v>15275117568</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>15274877103</v>
+        <v>15281447643</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>15280785625</v>
+        <v>15276424061</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>15280562893</v>
+        <v>15280271790</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>15281020296</v>
+        <v>15276474097</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>15281646010</v>
+        <v>15278908990</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>15273360637</v>
+        <v>15278144830</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>15271350668</v>
+        <v>15273729755</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>15282549133</v>
+        <v>15281911505</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>15276246412</v>
+        <v>15281333163</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>15278769409</v>
+        <v>15280732175</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>15280732951</v>
+        <v>15278833215</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>15279196672</v>
+        <v>15269733982</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>15282561502</v>
+        <v>15269428857</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>15281331903</v>
+        <v>15278341034</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>15283239581</v>
+        <v>15281132380</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>15277138206</v>
+        <v>15282301419</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>15278172608</v>
+        <v>15280499145</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>15278230161</v>
+        <v>15273266760</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>15279249349</v>
+        <v>15272387464</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>15280739039</v>
+        <v>15268903323</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>15282311576</v>
+        <v>15272549283</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>15279246078</v>
+        <v>15275882167</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>15280733098</v>
+        <v>15275606635</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>15282460769</v>
+        <v>15277945198</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>587038733</v>
+        <v>15279289017</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>15279998524</v>
+        <v>15279246078</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>15276821217</v>
+        <v>15281190198</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>15270781086</v>
+        <v>15280549157</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>15278207824</v>
+        <v>15276472661</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>15278537215</v>
+        <v>15272680107</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>15282200301</v>
+        <v>15280928184</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>15275650204</v>
+        <v>15270252618</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>15271364704</v>
+        <v>15270382927</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>15279138984</v>
+        <v>15270652901</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>15276624803</v>
+        <v>15274417059</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>15274176889</v>
+        <v>15278337540</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>15280922608</v>
+        <v>15279193371</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>15282268098</v>
+        <v>15280681386</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>15275370060</v>
+        <v>15281414677</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>15283043583</v>
+        <v>15269417011</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>15272776383</v>
+        <v>15277651732</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>15272033704</v>
+        <v>15275810209</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>15279900144</v>
+        <v>15284043705</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>15280822869</v>
+        <v>15281324665</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>15281277602</v>
+        <v>15280725396</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>15279648741</v>
+        <v>15283342414</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>15282535699</v>
+        <v>15281473683</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>15279681035</v>
+        <v>15282148182</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>15280826952</v>
+        <v>15282688157</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>15278872569</v>
+        <v>15280502882</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>15283166006</v>
+        <v>15281772965</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>15274984702</v>
+        <v>15281764706</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>15280703384</v>
+        <v>15281779278</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>15280738459</v>
+        <v>15281165587</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>15283731155</v>
+        <v>15282275717</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>15277899671</v>
+        <v>15270252487</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>15272384469</v>
+        <v>15276330921</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>15279372315</v>
+        <v>15274682313</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>15274823517</v>
+        <v>15271411674</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>15278205103</v>
+        <v>15281918832</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>15279110988</v>
+        <v>15272765657</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>15280602033</v>
+        <v>15271219238</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>15278967698</v>
+        <v>15275605076</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>15280457188</v>
+        <v>15282200301</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>15283721361</v>
+        <v>15282240866</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>15280959003</v>
+        <v>15282146885</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>15278431230</v>
+        <v>15268844193</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>15278451868</v>
+        <v>15280826952</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>15282327995</v>
+        <v>15269226775</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>15278478047</v>
+        <v>15283341372</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>15280691008</v>
+        <v>15278756166</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="n">
-        <v>15279249224</v>
+        <v>15276084154</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="n">
-        <v>15277914432</v>
+        <v>15277654658</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="n">
-        <v>15280336812</v>
+        <v>15282672704</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="n">
-        <v>15281291706</v>
+        <v>15279854927</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="n">
-        <v>15274970831</v>
+        <v>15281417022</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="n">
-        <v>15271508103</v>
+        <v>15271352219</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="n">
-        <v>15279251126</v>
+        <v>15280728971</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="n">
-        <v>15280373896</v>
+        <v>15270025028</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="n">
-        <v>15281026859</v>
+        <v>15281234189</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="n">
-        <v>15273731735</v>
+        <v>15270728153</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="n">
-        <v>15271053273</v>
+        <v>15275721392</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="n">
-        <v>15282259944</v>
+        <v>15281333901</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="n">
-        <v>15281021340</v>
+        <v>15284119546</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="n">
-        <v>15282303227</v>
+        <v>15277616869</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="n">
-        <v>15281158328</v>
+        <v>15271371603</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="n">
-        <v>15279293488</v>
+        <v>15281445850</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="n">
-        <v>15282430709</v>
+        <v>15281272702</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="n">
-        <v>15276784380</v>
+        <v>15281024636</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="n">
-        <v>15273805821</v>
+        <v>15280457188</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="n">
-        <v>15283288214</v>
+        <v>15280739022</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="n">
-        <v>15279630161</v>
+        <v>15279181235</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="n">
-        <v>15283903910</v>
+        <v>15279000913</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="n">
-        <v>15274412649</v>
+        <v>15280138708</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="n">
-        <v>15280500955</v>
+        <v>15272766488</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="n">
-        <v>15282686790</v>
+        <v>15280785625</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="n">
-        <v>15280497635</v>
+        <v>15282322025</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="n">
-        <v>15279914023</v>
+        <v>15281903756</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="n">
-        <v>15281589569</v>
+        <v>15270938006</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="n">
-        <v>15268903323</v>
+        <v>15273501191</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="n">
-        <v>15280242790</v>
+        <v>15281369651</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="n">
-        <v>15274984924</v>
+        <v>15273805821</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="n">
-        <v>15273660999</v>
+        <v>15276769808</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="n">
-        <v>15282267900</v>
+        <v>15279313348</v>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="n">
-        <v>15280811121</v>
+        <v>15281378757</v>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="n">
-        <v>15280928184</v>
+        <v>15274890283</v>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="n">
-        <v>15281911505</v>
+        <v>15270781086</v>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="n">
-        <v>15282688157</v>
+        <v>15276769595</v>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="n">
-        <v>15282245237</v>
+        <v>15275669431</v>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="n">
-        <v>15282202631</v>
+        <v>15280269880</v>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="n">
-        <v>15281333901</v>
+        <v>15281367321</v>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="n">
-        <v>15279249351</v>
+        <v>15283288214</v>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="n">
-        <v>15280703377</v>
+        <v>15279844739</v>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="n">
-        <v>15283883534</v>
+        <v>15278205103</v>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="n">
-        <v>15283343376</v>
+        <v>15280906487</v>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="n">
-        <v>15280824014</v>
+        <v>15271363334</v>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="n">
-        <v>15281378757</v>
+        <v>15280406952</v>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="n">
-        <v>15278699439</v>
+        <v>15280738523</v>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="n">
-        <v>15282269965</v>
+        <v>15278911724</v>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="n">
-        <v>15270252487</v>
+        <v>15270929195</v>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="n">
-        <v>15269638418</v>
+        <v>15279114294</v>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="n">
-        <v>15273333600</v>
+        <v>15282533862</v>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="n">
-        <v>15280764731</v>
+        <v>15280737284</v>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="n">
-        <v>15283342414</v>
+        <v>15282613812</v>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="n">
-        <v>15278878662</v>
+        <v>15275785410</v>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="n">
-        <v>15280695013</v>
+        <v>15280701337</v>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="n">
-        <v>15269972865</v>
+        <v>15277899671</v>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="n">
-        <v>15283334869</v>
+        <v>15281239006</v>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="n">
-        <v>15282486382</v>
+        <v>15277874186</v>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="n">
-        <v>15276624514</v>
+        <v>15273243511</v>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="n">
-        <v>15277077968</v>
+        <v>15270866725</v>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="n">
-        <v>15280184912</v>
+        <v>15273333600</v>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="n">
-        <v>15280956679</v>
+        <v>15276784380</v>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="n">
-        <v>15269667636</v>
+        <v>15280779151</v>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="n">
-        <v>15280271790</v>
+        <v>15274970829</v>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="n">
-        <v>15269764221</v>
+        <v>15281351909</v>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="n">
-        <v>15279409909</v>
+        <v>15278419786</v>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="n">
-        <v>15280742658</v>
+        <v>15280738425</v>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="n">
-        <v>15281011564</v>
+        <v>15278144919</v>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="n">
-        <v>15281132380</v>
+        <v>15272825081</v>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="n">
-        <v>15280123292</v>
+        <v>15282051753</v>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="n">
-        <v>15282275717</v>
+        <v>15280401699</v>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="n">
-        <v>15274500792</v>
+        <v>15276055352</v>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="n">
-        <v>15278824683</v>
+        <v>15280350456</v>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="n">
-        <v>15281230017</v>
+        <v>15281335502</v>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="n">
-        <v>15277139592</v>
+        <v>15281590903</v>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="n">
-        <v>15273020853</v>
+        <v>15281195411</v>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="n">
-        <v>15274470584</v>
+        <v>15281077062</v>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="n">
-        <v>15273703025</v>
+        <v>15269127403</v>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="n">
-        <v>15278096296</v>
+        <v>15281556395</v>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="n">
-        <v>15281333163</v>
+        <v>15283343376</v>
       </c>
     </row>
     <row r="247">
       <c r="A247" t="n">
-        <v>15278530436</v>
+        <v>15270441478</v>
       </c>
     </row>
     <row r="248">
       <c r="A248" t="n">
-        <v>15270211306</v>
+        <v>15277679772</v>
       </c>
     </row>
     <row r="249">
       <c r="A249" t="n">
-        <v>15276671584</v>
+        <v>15279497173</v>
       </c>
     </row>
     <row r="250">
       <c r="A250" t="n">
-        <v>15280728619</v>
+        <v>15280724860</v>
       </c>
     </row>
     <row r="251">
       <c r="A251" t="n">
-        <v>15280982536</v>
+        <v>15271703038</v>
       </c>
     </row>
     <row r="252">
       <c r="A252" t="n">
-        <v>15282016850</v>
+        <v>15273738707</v>
       </c>
     </row>
     <row r="253">
       <c r="A253" t="n">
-        <v>15281779278</v>
+        <v>15273513647</v>
       </c>
     </row>
     <row r="254">
       <c r="A254" t="n">
-        <v>15276472661</v>
+        <v>15280975236</v>
       </c>
     </row>
     <row r="255">
       <c r="A255" t="n">
-        <v>15276474097</v>
+        <v>15268383291</v>
       </c>
     </row>
     <row r="256">
       <c r="A256" t="n">
-        <v>15277079397</v>
+        <v>15279914023</v>
       </c>
     </row>
     <row r="257">
       <c r="A257" t="n">
-        <v>15278347937</v>
+        <v>15281516303</v>
       </c>
     </row>
     <row r="258">
       <c r="A258" t="n">
-        <v>15281873029</v>
+        <v>15282395666</v>
       </c>
     </row>
     <row r="259">
       <c r="A259" t="n">
-        <v>15281186778</v>
+        <v>15282896527</v>
       </c>
     </row>
     <row r="260">
       <c r="A260" t="n">
-        <v>15279751100</v>
+        <v>15282688051</v>
       </c>
     </row>
     <row r="261">
       <c r="A261" t="n">
-        <v>15278892986</v>
+        <v>15273333599</v>
       </c>
     </row>
     <row r="262">
       <c r="A262" t="n">
-        <v>15272850623</v>
+        <v>15275545818</v>
       </c>
     </row>
     <row r="263">
       <c r="A263" t="n">
-        <v>15282246295</v>
+        <v>15272850623</v>
       </c>
     </row>
     <row r="264">
       <c r="A264" t="n">
-        <v>15269764314</v>
+        <v>15281021340</v>
       </c>
     </row>
     <row r="265">
       <c r="A265" t="n">
-        <v>15278973693</v>
+        <v>15282378677</v>
       </c>
     </row>
     <row r="266">
       <c r="A266" t="n">
-        <v>15270464085</v>
+        <v>15272184142</v>
       </c>
     </row>
     <row r="267">
       <c r="A267" t="n">
-        <v>15273513647</v>
+        <v>15276671586</v>
       </c>
     </row>
     <row r="268">
       <c r="A268" t="n">
-        <v>15273243511</v>
+        <v>15271200646</v>
       </c>
     </row>
     <row r="269">
       <c r="A269" t="n">
-        <v>15281629232</v>
+        <v>15267970098</v>
       </c>
     </row>
     <row r="270">
       <c r="A270" t="n">
-        <v>15277669216</v>
+        <v>15272001943</v>
       </c>
     </row>
     <row r="271">
       <c r="A271" t="n">
-        <v>15281370834</v>
+        <v>15279955789</v>
       </c>
     </row>
     <row r="272">
       <c r="A272" t="n">
-        <v>15273987341</v>
+        <v>15279911560</v>
       </c>
     </row>
     <row r="273">
       <c r="A273" t="n">
-        <v>15276671586</v>
+        <v>15279314061</v>
       </c>
     </row>
     <row r="274">
       <c r="A274" t="n">
-        <v>15278944944</v>
+        <v>15272591482</v>
       </c>
     </row>
     <row r="275">
       <c r="A275" t="n">
-        <v>15271526633</v>
+        <v>15278172741</v>
       </c>
     </row>
     <row r="276">
       <c r="A276" t="n">
-        <v>15278474453</v>
+        <v>15283351569</v>
       </c>
     </row>
     <row r="277">
       <c r="A277" t="n">
-        <v>15276835424</v>
+        <v>15280355547</v>
       </c>
     </row>
     <row r="278">
       <c r="A278" t="n">
-        <v>15280370860</v>
+        <v>15278348214</v>
       </c>
     </row>
     <row r="279">
       <c r="A279" t="n">
-        <v>15280450647</v>
+        <v>15280243805</v>
       </c>
     </row>
     <row r="280">
       <c r="A280" t="n">
-        <v>15282730302</v>
+        <v>15282331885</v>
       </c>
     </row>
     <row r="281">
       <c r="A281" t="n">
-        <v>15278010880</v>
+        <v>15278451907</v>
       </c>
     </row>
     <row r="282">
       <c r="A282" t="n">
-        <v>15268169332</v>
+        <v>15273731880</v>
       </c>
     </row>
     <row r="283">
       <c r="A283" t="n">
-        <v>15282234574</v>
+        <v>15276519638</v>
       </c>
     </row>
     <row r="284">
       <c r="A284" t="n">
-        <v>15273888072</v>
+        <v>15268559158</v>
       </c>
     </row>
     <row r="285">
       <c r="A285" t="n">
-        <v>15278517314</v>
+        <v>15279751973</v>
       </c>
     </row>
     <row r="286">
       <c r="A286" t="n">
-        <v>15281556395</v>
+        <v>15283068940</v>
       </c>
     </row>
     <row r="287">
       <c r="A287" t="n">
-        <v>15281988928</v>
+        <v>15280815542</v>
       </c>
     </row>
     <row r="288">
       <c r="A288" t="n">
-        <v>15283103350</v>
+        <v>15278230161</v>
       </c>
     </row>
     <row r="289">
       <c r="A289" t="n">
-        <v>15269947154</v>
+        <v>15280823679</v>
       </c>
     </row>
     <row r="290">
       <c r="A290" t="n">
-        <v>15274890218</v>
+        <v>15278546547</v>
       </c>
     </row>
     <row r="291">
       <c r="A291" t="n">
-        <v>15279254790</v>
+        <v>15282549133</v>
       </c>
     </row>
     <row r="292">
       <c r="A292" t="n">
-        <v>15281270387</v>
+        <v>15270211306</v>
       </c>
     </row>
     <row r="293">
       <c r="A293" t="n">
-        <v>15273564998</v>
+        <v>15278537215</v>
       </c>
     </row>
     <row r="294">
       <c r="A294" t="n">
-        <v>15277914481</v>
+        <v>15275882189</v>
       </c>
     </row>
     <row r="295">
       <c r="A295" t="n">
-        <v>15268557452</v>
+        <v>15272184144</v>
       </c>
     </row>
     <row r="296">
       <c r="A296" t="n">
-        <v>15278946510</v>
+        <v>15279114785</v>
       </c>
     </row>
     <row r="297">
       <c r="A297" t="n">
-        <v>15270424028</v>
+        <v>15280242790</v>
       </c>
     </row>
     <row r="298">
       <c r="A298" t="n">
-        <v>15282420846</v>
+        <v>15281667468</v>
       </c>
     </row>
     <row r="299">
       <c r="A299" t="n">
-        <v>15275882189</v>
+        <v>15278973693</v>
       </c>
     </row>
     <row r="300">
       <c r="A300" t="n">
-        <v>15276088246</v>
+        <v>15282966257</v>
       </c>
     </row>
     <row r="301">
       <c r="A301" t="n">
-        <v>15268143667</v>
+        <v>15281082651</v>
       </c>
     </row>
     <row r="302">
       <c r="A302" t="n">
-        <v>15281326593</v>
+        <v>15276153920</v>
       </c>
     </row>
     <row r="303">
       <c r="A303" t="n">
-        <v>15282237274</v>
+        <v>15274877103</v>
       </c>
     </row>
     <row r="304">
       <c r="A304" t="n">
-        <v>15282743297</v>
+        <v>15282386580</v>
       </c>
     </row>
     <row r="305">
       <c r="A305" t="n">
-        <v>15279484646</v>
+        <v>15274984702</v>
       </c>
     </row>
     <row r="306">
       <c r="A306" t="n">
-        <v>15280871680</v>
+        <v>15274176889</v>
       </c>
     </row>
     <row r="307">
       <c r="A307" t="n">
-        <v>15280243805</v>
+        <v>15271508103</v>
       </c>
     </row>
     <row r="308">
       <c r="A308" t="n">
-        <v>15275800786</v>
+        <v>15270424028</v>
       </c>
     </row>
     <row r="309">
       <c r="A309" t="n">
-        <v>15277874186</v>
+        <v>15270643829</v>
       </c>
     </row>
     <row r="310">
       <c r="A310" t="n">
-        <v>15277651732</v>
+        <v>15281018961</v>
       </c>
     </row>
     <row r="311">
       <c r="A311" t="n">
-        <v>15279911560</v>
+        <v>15281443639</v>
       </c>
     </row>
     <row r="312">
       <c r="A312" t="n">
-        <v>15281190008</v>
+        <v>15278893879</v>
       </c>
     </row>
     <row r="313">
       <c r="A313" t="n">
-        <v>15273729755</v>
+        <v>15278419156</v>
       </c>
     </row>
     <row r="314">
       <c r="A314" t="n">
-        <v>15280869322</v>
+        <v>15274500792</v>
       </c>
     </row>
     <row r="315">
       <c r="A315" t="n">
-        <v>15281918832</v>
+        <v>15278434241</v>
       </c>
     </row>
     <row r="316">
       <c r="A316" t="n">
-        <v>15282688051</v>
+        <v>15280728619</v>
       </c>
     </row>
     <row r="317">
       <c r="A317" t="n">
-        <v>15276428461</v>
+        <v>15281413587</v>
       </c>
     </row>
     <row r="318">
       <c r="A318" t="n">
-        <v>15278699629</v>
+        <v>15270061416</v>
       </c>
     </row>
     <row r="319">
       <c r="A319" t="n">
-        <v>15277839605</v>
+        <v>15275800789</v>
       </c>
     </row>
     <row r="320">
       <c r="A320" t="n">
-        <v>15282735021</v>
+        <v>15268557452</v>
       </c>
     </row>
     <row r="321">
       <c r="A321" t="n">
-        <v>15279773259</v>
+        <v>15278646969</v>
       </c>
     </row>
     <row r="322">
       <c r="A322" t="n">
-        <v>15277296786</v>
+        <v>15278956796</v>
       </c>
     </row>
     <row r="323">
       <c r="A323" t="n">
-        <v>15279759471</v>
+        <v>15282093284</v>
       </c>
     </row>
     <row r="324">
       <c r="A324" t="n">
-        <v>15279193371</v>
+        <v>15283103350</v>
       </c>
     </row>
     <row r="325">
       <c r="A325" t="n">
-        <v>15281082651</v>
+        <v>15271645488</v>
       </c>
     </row>
     <row r="326">
       <c r="A326" t="n">
-        <v>15283351569</v>
+        <v>15279235586</v>
       </c>
     </row>
     <row r="327">
       <c r="A327" t="n">
-        <v>15270728153</v>
+        <v>15280738479</v>
       </c>
     </row>
     <row r="328">
       <c r="A328" t="n">
-        <v>15283322381</v>
+        <v>15272271524</v>
       </c>
     </row>
     <row r="329">
       <c r="A329" t="n">
-        <v>15282146885</v>
+        <v>15280237193</v>
       </c>
     </row>
     <row r="330">
       <c r="A330" t="n">
-        <v>15275281476</v>
+        <v>15280370860</v>
       </c>
     </row>
     <row r="331">
       <c r="A331" t="n">
-        <v>15278911724</v>
+        <v>15268936431</v>
       </c>
     </row>
     <row r="332">
       <c r="A332" t="n">
-        <v>15279680226</v>
+        <v>15280766703</v>
       </c>
     </row>
     <row r="333">
       <c r="A333" t="n">
-        <v>15281879492</v>
+        <v>15281011564</v>
       </c>
     </row>
     <row r="334">
       <c r="A334" t="n">
-        <v>15276907927</v>
+        <v>15276428461</v>
       </c>
     </row>
     <row r="335">
       <c r="A335" t="n">
-        <v>15276424061</v>
+        <v>15282296485</v>
       </c>
     </row>
     <row r="336">
       <c r="A336" t="n">
-        <v>15279090322</v>
+        <v>15277945199</v>
       </c>
     </row>
     <row r="337">
       <c r="A337" t="n">
-        <v>15283334853</v>
+        <v>15282237274</v>
       </c>
     </row>
     <row r="338">
       <c r="A338" t="n">
-        <v>15279681274</v>
+        <v>15273360637</v>
       </c>
     </row>
     <row r="339">
       <c r="A339" t="n">
-        <v>15270866725</v>
+        <v>15282334932</v>
       </c>
     </row>
     <row r="340">
       <c r="A340" t="n">
-        <v>15278419786</v>
+        <v>15281714394</v>
       </c>
     </row>
     <row r="341">
       <c r="A341" t="n">
-        <v>15281674909</v>
+        <v>15273888402</v>
       </c>
     </row>
     <row r="342">
@@ -2142,462 +2142,462 @@
     </row>
     <row r="343">
       <c r="A343" t="n">
-        <v>15270360466</v>
+        <v>15280742658</v>
       </c>
     </row>
     <row r="344">
       <c r="A344" t="n">
-        <v>15278967938</v>
+        <v>15281028298</v>
       </c>
     </row>
     <row r="345">
       <c r="A345" t="n">
-        <v>15280962783</v>
+        <v>15269949238</v>
       </c>
     </row>
     <row r="346">
       <c r="A346" t="n">
-        <v>15276784379</v>
+        <v>15277945157</v>
       </c>
     </row>
     <row r="347">
       <c r="A347" t="n">
-        <v>15281077062</v>
+        <v>15280336812</v>
       </c>
     </row>
     <row r="348">
       <c r="A348" t="n">
-        <v>15278434241</v>
+        <v>15269190347</v>
       </c>
     </row>
     <row r="349">
       <c r="A349" t="n">
-        <v>15280453854</v>
+        <v>15279702146</v>
       </c>
     </row>
     <row r="350">
       <c r="A350" t="n">
-        <v>15283341372</v>
+        <v>15278824683</v>
       </c>
     </row>
     <row r="351">
       <c r="A351" t="n">
-        <v>15283475493</v>
+        <v>15282852697</v>
       </c>
     </row>
     <row r="352">
       <c r="A352" t="n">
-        <v>15282471994</v>
+        <v>15274890218</v>
       </c>
     </row>
     <row r="353">
       <c r="A353" t="n">
-        <v>15279844739</v>
+        <v>15279751100</v>
       </c>
     </row>
     <row r="354">
       <c r="A354" t="n">
-        <v>15276042545</v>
+        <v>15276862162</v>
       </c>
     </row>
     <row r="355">
       <c r="A355" t="n">
-        <v>15281239006</v>
+        <v>15284009498</v>
       </c>
     </row>
     <row r="356">
       <c r="A356" t="n">
-        <v>15277266398</v>
+        <v>15280924850</v>
       </c>
     </row>
     <row r="357">
       <c r="A357" t="n">
-        <v>15279289017</v>
+        <v>15283239581</v>
       </c>
     </row>
     <row r="358">
       <c r="A358" t="n">
-        <v>15267970098</v>
+        <v>15277101734</v>
       </c>
     </row>
     <row r="359">
       <c r="A359" t="n">
-        <v>15280587105</v>
+        <v>15282259944</v>
       </c>
     </row>
     <row r="360">
       <c r="A360" t="n">
-        <v>15274970829</v>
+        <v>15272552656</v>
       </c>
     </row>
     <row r="361">
       <c r="A361" t="n">
-        <v>15280823679</v>
+        <v>15280811121</v>
       </c>
     </row>
     <row r="362">
       <c r="A362" t="n">
-        <v>15282597869</v>
+        <v>15273667031</v>
       </c>
     </row>
     <row r="363">
       <c r="A363" t="n">
-        <v>15280372180</v>
+        <v>15279379522</v>
       </c>
     </row>
     <row r="364">
       <c r="A364" t="n">
-        <v>15282386548</v>
+        <v>15269972865</v>
       </c>
     </row>
     <row r="365">
       <c r="A365" t="n">
-        <v>15274890236</v>
+        <v>15275945656</v>
       </c>
     </row>
     <row r="366">
       <c r="A366" t="n">
-        <v>15276518476</v>
+        <v>15279061619</v>
       </c>
     </row>
     <row r="367">
       <c r="A367" t="n">
-        <v>15282240866</v>
+        <v>15276117881</v>
       </c>
     </row>
     <row r="368">
       <c r="A368" t="n">
-        <v>15270769946</v>
+        <v>15269638418</v>
       </c>
     </row>
     <row r="369">
       <c r="A369" t="n">
-        <v>15278144919</v>
+        <v>15279090280</v>
       </c>
     </row>
     <row r="370">
       <c r="A370" t="n">
-        <v>15280238394</v>
+        <v>15277669216</v>
       </c>
     </row>
     <row r="371">
       <c r="A371" t="n">
-        <v>15275705450</v>
+        <v>15281184068</v>
       </c>
     </row>
     <row r="372">
       <c r="A372" t="n">
-        <v>15279003866</v>
+        <v>15273429555</v>
       </c>
     </row>
     <row r="373">
       <c r="A373" t="n">
-        <v>15284119546</v>
+        <v>15276428457</v>
       </c>
     </row>
     <row r="374">
       <c r="A374" t="n">
-        <v>15270459133</v>
+        <v>15278010880</v>
       </c>
     </row>
     <row r="375">
       <c r="A375" t="n">
-        <v>15281369651</v>
+        <v>15284463792</v>
       </c>
     </row>
     <row r="376">
       <c r="A376" t="n">
-        <v>15280129574</v>
+        <v>15282500664</v>
       </c>
     </row>
     <row r="377">
       <c r="A377" t="n">
-        <v>15282296485</v>
+        <v>15279681034</v>
       </c>
     </row>
     <row r="378">
       <c r="A378" t="n">
-        <v>15271448058</v>
+        <v>15281326593</v>
       </c>
     </row>
     <row r="379">
       <c r="A379" t="n">
-        <v>15270025028</v>
+        <v>15276784379</v>
       </c>
     </row>
     <row r="380">
       <c r="A380" t="n">
-        <v>15268936431</v>
+        <v>15269207070</v>
       </c>
     </row>
     <row r="381">
       <c r="A381" t="n">
-        <v>15278419156</v>
+        <v>15282968321</v>
       </c>
     </row>
     <row r="382">
       <c r="A382" t="n">
-        <v>15279681361</v>
+        <v>15282535699</v>
       </c>
     </row>
     <row r="383">
       <c r="A383" t="n">
-        <v>15275314240</v>
+        <v>15270840531</v>
       </c>
     </row>
     <row r="384">
       <c r="A384" t="n">
-        <v>15280822101</v>
+        <v>15280553889</v>
       </c>
     </row>
     <row r="385">
       <c r="A385" t="n">
-        <v>15277844546</v>
+        <v>15277914481</v>
       </c>
     </row>
     <row r="386">
       <c r="A386" t="n">
-        <v>15269949061</v>
+        <v>15282501599</v>
       </c>
     </row>
     <row r="387">
       <c r="A387" t="n">
-        <v>15279804921</v>
+        <v>15281158328</v>
       </c>
     </row>
     <row r="388">
       <c r="A388" t="n">
-        <v>15280672553</v>
+        <v>15281336121</v>
       </c>
     </row>
     <row r="389">
       <c r="A389" t="n">
-        <v>15284496037</v>
+        <v>15274984924</v>
       </c>
     </row>
     <row r="390">
       <c r="A390" t="n">
-        <v>15271986349</v>
+        <v>15282335222</v>
       </c>
     </row>
     <row r="391">
       <c r="A391" t="n">
-        <v>15274824201</v>
+        <v>15280123292</v>
       </c>
     </row>
     <row r="392">
       <c r="A392" t="n">
-        <v>15280889466</v>
+        <v>15283411918</v>
       </c>
     </row>
     <row r="393">
       <c r="A393" t="n">
-        <v>15281772965</v>
+        <v>15277056765</v>
       </c>
     </row>
     <row r="394">
       <c r="A394" t="n">
-        <v>15281272702</v>
+        <v>15273021190</v>
       </c>
     </row>
     <row r="395">
       <c r="A395" t="n">
-        <v>15277804412</v>
+        <v>15271122455</v>
       </c>
     </row>
     <row r="396">
       <c r="A396" t="n">
-        <v>15278157816</v>
+        <v>15273277312</v>
       </c>
     </row>
     <row r="397">
       <c r="A397" t="n">
-        <v>15269650228</v>
+        <v>15274739297</v>
       </c>
     </row>
     <row r="398">
       <c r="A398" t="n">
-        <v>15279952250</v>
+        <v>15271364704</v>
       </c>
     </row>
     <row r="399">
       <c r="A399" t="n">
-        <v>15269705348</v>
+        <v>15276057417</v>
       </c>
     </row>
     <row r="400">
       <c r="A400" t="n">
-        <v>15270804417</v>
+        <v>15272767006</v>
       </c>
     </row>
     <row r="401">
       <c r="A401" t="n">
-        <v>15280725396</v>
+        <v>15280421118</v>
       </c>
     </row>
     <row r="402">
       <c r="A402" t="n">
-        <v>15270941674</v>
+        <v>15277678714</v>
       </c>
     </row>
     <row r="403">
       <c r="A403" t="n">
-        <v>15275669431</v>
+        <v>15277138206</v>
       </c>
     </row>
     <row r="404">
       <c r="A404" t="n">
-        <v>15281352665</v>
+        <v>15281270387</v>
       </c>
     </row>
     <row r="405">
       <c r="A405" t="n">
-        <v>15275544775</v>
+        <v>15281026859</v>
       </c>
     </row>
     <row r="406">
       <c r="A406" t="n">
-        <v>15271087770</v>
+        <v>15270875337</v>
       </c>
     </row>
     <row r="407">
       <c r="A407" t="n">
-        <v>15284454314</v>
+        <v>15280689543</v>
       </c>
     </row>
     <row r="408">
       <c r="A408" t="n">
-        <v>15271016520</v>
+        <v>15281186778</v>
       </c>
     </row>
     <row r="409">
       <c r="A409" t="n">
-        <v>15279110817</v>
+        <v>15270831378</v>
       </c>
     </row>
     <row r="410">
       <c r="A410" t="n">
-        <v>15276862162</v>
+        <v>15270111470</v>
       </c>
     </row>
     <row r="411">
       <c r="A411" t="n">
-        <v>15282390126</v>
+        <v>15280594997</v>
       </c>
     </row>
     <row r="412">
       <c r="A412" t="n">
-        <v>15281443639</v>
+        <v>15278412691</v>
       </c>
     </row>
     <row r="413">
       <c r="A413" t="n">
-        <v>15273872823</v>
+        <v>15280402311</v>
       </c>
     </row>
     <row r="414">
       <c r="A414" t="n">
-        <v>15276136426</v>
+        <v>15283343393</v>
       </c>
     </row>
     <row r="415">
       <c r="A415" t="n">
-        <v>15280641703</v>
+        <v>15281424218</v>
       </c>
     </row>
     <row r="416">
       <c r="A416" t="n">
-        <v>15282296512</v>
+        <v>15278774814</v>
       </c>
     </row>
     <row r="417">
       <c r="A417" t="n">
-        <v>15276424033</v>
+        <v>15275071001</v>
       </c>
     </row>
     <row r="418">
       <c r="A418" t="n">
-        <v>15270252618</v>
+        <v>15271393867</v>
       </c>
     </row>
     <row r="419">
       <c r="A419" t="n">
-        <v>15271468310</v>
+        <v>15279003866</v>
       </c>
     </row>
     <row r="420">
       <c r="A420" t="n">
-        <v>15277139099</v>
+        <v>15280224399</v>
       </c>
     </row>
     <row r="421">
       <c r="A421" t="n">
-        <v>15279365654</v>
+        <v>15283475493</v>
       </c>
     </row>
     <row r="422">
       <c r="A422" t="n">
-        <v>15284110340</v>
+        <v>15271448797</v>
       </c>
     </row>
     <row r="423">
       <c r="A423" t="n">
-        <v>15268383291</v>
+        <v>15275606489</v>
       </c>
     </row>
     <row r="424">
       <c r="A424" t="n">
-        <v>15266967144</v>
+        <v>15273731735</v>
       </c>
     </row>
     <row r="425">
       <c r="A425" t="n">
-        <v>15282331885</v>
+        <v>15280978307</v>
       </c>
     </row>
     <row r="426">
       <c r="A426" t="n">
-        <v>15280974033</v>
+        <v>15279565932</v>
       </c>
     </row>
     <row r="427">
       <c r="A427" t="n">
-        <v>15283103312</v>
+        <v>15271016520</v>
       </c>
     </row>
     <row r="428">
       <c r="A428" t="n">
-        <v>15279252082</v>
+        <v>15282471874</v>
       </c>
     </row>
     <row r="429">
       <c r="A429" t="n">
-        <v>15274877104</v>
+        <v>15279409909</v>
       </c>
     </row>
     <row r="430">
       <c r="A430" t="n">
-        <v>15282471976</v>
+        <v>15271453437</v>
       </c>
     </row>
     <row r="431">
       <c r="A431" t="n">
-        <v>15272825081</v>
+        <v>15279110988</v>
       </c>
     </row>
     <row r="432">
       <c r="A432" t="n">
-        <v>15271525049</v>
+        <v>15268179642</v>
       </c>
     </row>
     <row r="433">
       <c r="A433" t="n">
-        <v>15284043705</v>
+        <v>15283236753</v>
       </c>
     </row>
     <row r="434">
       <c r="A434" t="n">
-        <v>15276830184</v>
+        <v>15273640584</v>
       </c>
     </row>
     <row r="435">
@@ -2607,2125 +2607,2128 @@
     </row>
     <row r="436">
       <c r="A436" t="n">
-        <v>15268179642</v>
+        <v>15278944944</v>
       </c>
     </row>
     <row r="437">
       <c r="A437" t="n">
-        <v>15275902197</v>
+        <v>15273667038</v>
       </c>
     </row>
     <row r="438">
       <c r="A438" t="n">
-        <v>15282093284</v>
+        <v>15276821217</v>
       </c>
     </row>
     <row r="439">
       <c r="A439" t="n">
-        <v>15274417059</v>
+        <v>15280373896</v>
       </c>
     </row>
     <row r="440">
       <c r="A440" t="n">
-        <v>15277654658</v>
+        <v>15279804921</v>
       </c>
     </row>
     <row r="441">
       <c r="A441" t="n">
-        <v>15280732175</v>
+        <v>15280927056</v>
       </c>
     </row>
     <row r="442">
       <c r="A442" t="n">
-        <v>15278833215</v>
+        <v>15280450769</v>
       </c>
     </row>
     <row r="443">
       <c r="A443" t="n">
-        <v>15278172741</v>
+        <v>15281330161</v>
       </c>
     </row>
     <row r="444">
       <c r="A444" t="n">
-        <v>15271448797</v>
+        <v>15271986349</v>
       </c>
     </row>
     <row r="445">
       <c r="A445" t="n">
-        <v>15278011111</v>
+        <v>15272948091</v>
       </c>
     </row>
     <row r="446">
       <c r="A446" t="n">
-        <v>15278412691</v>
+        <v>15273638582</v>
       </c>
     </row>
     <row r="447">
       <c r="A447" t="n">
-        <v>15280571941</v>
+        <v>15276518476</v>
       </c>
     </row>
     <row r="448">
       <c r="A448" t="n">
-        <v>15281324665</v>
+        <v>15272725121</v>
       </c>
     </row>
     <row r="449">
       <c r="A449" t="n">
-        <v>15273021190</v>
+        <v>15270337938</v>
       </c>
     </row>
     <row r="450">
       <c r="A450" t="n">
-        <v>15282538492</v>
+        <v>15282339837</v>
       </c>
     </row>
     <row r="451">
       <c r="A451" t="n">
-        <v>15282856978</v>
+        <v>15281666842</v>
       </c>
     </row>
     <row r="452">
       <c r="A452" t="n">
-        <v>15271363334</v>
+        <v>15277077968</v>
       </c>
     </row>
     <row r="453">
       <c r="A453" t="n">
-        <v>15278348214</v>
+        <v>15272097850</v>
       </c>
     </row>
     <row r="454">
       <c r="A454" t="n">
-        <v>15273667038</v>
+        <v>15278172608</v>
       </c>
     </row>
     <row r="455">
       <c r="A455" t="n">
-        <v>15271188869</v>
+        <v>15273660999</v>
       </c>
     </row>
     <row r="456">
       <c r="A456" t="n">
-        <v>15275566146</v>
+        <v>15275260003</v>
       </c>
     </row>
     <row r="457">
       <c r="A457" t="n">
-        <v>15278172609</v>
+        <v>15277654978</v>
       </c>
     </row>
     <row r="458">
       <c r="A458" t="n">
-        <v>15282409069</v>
+        <v>15278451868</v>
       </c>
     </row>
     <row r="459">
       <c r="A459" t="n">
-        <v>15282813092</v>
+        <v>15280571941</v>
       </c>
     </row>
     <row r="460">
       <c r="A460" t="n">
-        <v>15279770983</v>
+        <v>15283355934</v>
       </c>
     </row>
     <row r="461">
       <c r="A461" t="n">
-        <v>15268251122</v>
+        <v>15282234574</v>
       </c>
     </row>
     <row r="462">
       <c r="A462" t="n">
-        <v>15281416970</v>
+        <v>15277698537</v>
       </c>
     </row>
     <row r="463">
       <c r="A463" t="n">
-        <v>15281473683</v>
+        <v>15279293488</v>
       </c>
     </row>
     <row r="464">
       <c r="A464" t="n">
-        <v>15282896527</v>
+        <v>15276472663</v>
       </c>
     </row>
     <row r="465">
       <c r="A465" t="n">
-        <v>15277679772</v>
+        <v>15271527819</v>
       </c>
     </row>
     <row r="466">
       <c r="A466" t="n">
-        <v>15279305425</v>
+        <v>15283341665</v>
       </c>
     </row>
     <row r="467">
       <c r="A467" t="n">
-        <v>15280465197</v>
+        <v>15268236400</v>
       </c>
     </row>
     <row r="468">
       <c r="A468" t="n">
-        <v>15280403344</v>
+        <v>15277239776</v>
       </c>
     </row>
     <row r="469">
       <c r="A469" t="n">
-        <v>15278434223</v>
+        <v>15274450986</v>
       </c>
     </row>
     <row r="470">
       <c r="A470" t="n">
-        <v>15273275702</v>
+        <v>15278494558</v>
       </c>
     </row>
     <row r="471">
       <c r="A471" t="n">
-        <v>15280927056</v>
+        <v>15279422207</v>
       </c>
     </row>
     <row r="472">
       <c r="A472" t="n">
-        <v>15281633615</v>
+        <v>15280562893</v>
       </c>
     </row>
     <row r="473">
       <c r="A473" t="n">
-        <v>15274890204</v>
+        <v>15279409656</v>
       </c>
     </row>
     <row r="474">
       <c r="A474" t="n">
-        <v>15270643829</v>
+        <v>15271023824</v>
       </c>
     </row>
     <row r="475">
       <c r="A475" t="n">
-        <v>15272271524</v>
+        <v>15281666025</v>
       </c>
     </row>
     <row r="476">
       <c r="A476" t="n">
-        <v>15274485562</v>
+        <v>15279061766</v>
       </c>
     </row>
     <row r="477">
       <c r="A477" t="n">
-        <v>15279484648</v>
+        <v>15282016850</v>
       </c>
     </row>
     <row r="478">
       <c r="A478" t="n">
-        <v>15272591482</v>
+        <v>15277839605</v>
       </c>
     </row>
     <row r="479">
       <c r="A479" t="n">
-        <v>15280138708</v>
+        <v>15281164468</v>
       </c>
     </row>
     <row r="480">
       <c r="A480" t="n">
-        <v>15272591142</v>
+        <v>15275272586</v>
       </c>
     </row>
     <row r="481">
       <c r="A481" t="n">
-        <v>15275800789</v>
+        <v>15274767088</v>
       </c>
     </row>
     <row r="482">
       <c r="A482" t="n">
-        <v>15283096042</v>
+        <v>15280822101</v>
       </c>
     </row>
     <row r="483">
       <c r="A483" t="n">
-        <v>15272850253</v>
+        <v>15269667636</v>
       </c>
     </row>
     <row r="484">
       <c r="A484" t="n">
-        <v>15278956796</v>
+        <v>15274470584</v>
       </c>
     </row>
     <row r="485">
       <c r="A485" t="n">
-        <v>15276472663</v>
+        <v>15271526633</v>
       </c>
     </row>
     <row r="486">
       <c r="A486" t="n">
-        <v>15281417022</v>
+        <v>15271002528</v>
       </c>
     </row>
     <row r="487">
       <c r="A487" t="n">
-        <v>15279652746</v>
+        <v>15278904343</v>
       </c>
     </row>
     <row r="488">
       <c r="A488" t="n">
-        <v>15271371603</v>
+        <v>15275800786</v>
       </c>
     </row>
     <row r="489">
       <c r="A489" t="n">
-        <v>15280549157</v>
+        <v>15281629232</v>
       </c>
     </row>
     <row r="490">
       <c r="A490" t="n">
-        <v>15279422137</v>
+        <v>15268251122</v>
       </c>
     </row>
     <row r="491">
       <c r="A491" t="n">
-        <v>15273333599</v>
+        <v>15280637573</v>
       </c>
     </row>
     <row r="492">
       <c r="A492" t="n">
-        <v>15271200646</v>
+        <v>15271188869</v>
       </c>
     </row>
     <row r="493">
       <c r="A493" t="n">
-        <v>15277056765</v>
+        <v>15274485562</v>
       </c>
     </row>
     <row r="494">
       <c r="A494" t="n">
-        <v>15281406342</v>
+        <v>15280703377</v>
       </c>
     </row>
     <row r="495">
       <c r="A495" t="n">
-        <v>15280681386</v>
+        <v>15283096155</v>
       </c>
     </row>
     <row r="496">
       <c r="A496" t="n">
-        <v>15269733982</v>
+        <v>15280695013</v>
       </c>
     </row>
     <row r="497">
       <c r="A497" t="n">
-        <v>15273509085</v>
+        <v>15281165693</v>
       </c>
     </row>
     <row r="498">
       <c r="A498" t="n">
-        <v>15270024354</v>
+        <v>15279305425</v>
       </c>
     </row>
     <row r="499">
       <c r="A499" t="n">
-        <v>15279744659</v>
+        <v>15271923861</v>
       </c>
     </row>
     <row r="500">
       <c r="A500" t="n">
-        <v>15270337938</v>
+        <v>15272193128</v>
       </c>
     </row>
     <row r="501">
       <c r="A501" t="n">
-        <v>15279702626</v>
+        <v>15280881791</v>
       </c>
     </row>
     <row r="502">
       <c r="A502" t="n">
-        <v>15279168595</v>
+        <v>15280641703</v>
       </c>
     </row>
     <row r="503">
       <c r="A503" t="n">
-        <v>15276464257</v>
+        <v>15268215653</v>
       </c>
     </row>
     <row r="504">
       <c r="A504" t="n">
-        <v>15279681034</v>
+        <v>15274890204</v>
       </c>
     </row>
     <row r="505">
       <c r="A505" t="n">
-        <v>15277709912</v>
+        <v>15275566146</v>
       </c>
     </row>
     <row r="506">
       <c r="A506" t="n">
-        <v>15279235586</v>
+        <v>15280450647</v>
       </c>
     </row>
     <row r="507">
       <c r="A507" t="n">
-        <v>15277913805</v>
+        <v>15283096042</v>
       </c>
     </row>
     <row r="508">
       <c r="A508" t="n">
-        <v>15280766703</v>
+        <v>15279110817</v>
       </c>
     </row>
     <row r="509">
       <c r="A509" t="n">
-        <v>15275328011</v>
+        <v>15269764314</v>
       </c>
     </row>
     <row r="510">
       <c r="A510" t="n">
-        <v>15269786513</v>
+        <v>15269947154</v>
       </c>
     </row>
     <row r="511">
       <c r="A511" t="n">
-        <v>15280239355</v>
+        <v>15277874196</v>
       </c>
     </row>
     <row r="512">
       <c r="A512" t="n">
-        <v>15282293862</v>
+        <v>15280703384</v>
       </c>
     </row>
     <row r="513">
       <c r="A513" t="n">
-        <v>15281714394</v>
+        <v>15282202631</v>
       </c>
     </row>
     <row r="514">
       <c r="A514" t="n">
-        <v>15271989345</v>
+        <v>15282420846</v>
       </c>
     </row>
     <row r="515">
       <c r="A515" t="n">
-        <v>15282734582</v>
+        <v>15280497635</v>
       </c>
     </row>
     <row r="516">
       <c r="A516" t="n">
-        <v>15276055352</v>
+        <v>15275247304</v>
       </c>
     </row>
     <row r="517">
       <c r="A517" t="n">
-        <v>15284009498</v>
+        <v>15283322381</v>
       </c>
     </row>
     <row r="518">
       <c r="A518" t="n">
-        <v>15280738425</v>
+        <v>15270804417</v>
       </c>
     </row>
     <row r="519">
       <c r="A519" t="n">
-        <v>15274682313</v>
+        <v>15277860727</v>
       </c>
     </row>
     <row r="520">
       <c r="A520" t="n">
-        <v>587053093</v>
+        <v>15269968201</v>
       </c>
     </row>
     <row r="521">
       <c r="A521" t="n">
-        <v>15281628958</v>
+        <v>15280073374</v>
       </c>
     </row>
     <row r="522">
       <c r="A522" t="n">
-        <v>15279479439</v>
+        <v>15282269965</v>
       </c>
     </row>
     <row r="523">
       <c r="A523" t="n">
-        <v>15275705449</v>
+        <v>15275544775</v>
       </c>
     </row>
     <row r="524">
       <c r="A524" t="n">
-        <v>15274471102</v>
+        <v>15281352665</v>
       </c>
     </row>
     <row r="525">
       <c r="A525" t="n">
-        <v>15271393867</v>
+        <v>15279759471</v>
       </c>
     </row>
     <row r="526">
       <c r="A526" t="n">
-        <v>15273699941</v>
+        <v>15279716510</v>
       </c>
     </row>
     <row r="527">
       <c r="A527" t="n">
-        <v>15280421118</v>
+        <v>15269786539</v>
       </c>
     </row>
     <row r="528">
       <c r="A528" t="n">
-        <v>15280738523</v>
+        <v>15280869322</v>
       </c>
     </row>
     <row r="529">
       <c r="A529" t="n">
-        <v>15271645488</v>
+        <v>15272591142</v>
       </c>
     </row>
     <row r="530">
       <c r="A530" t="n">
-        <v>15281763779</v>
+        <v>15277844546</v>
       </c>
     </row>
     <row r="531">
       <c r="A531" t="n">
-        <v>15284463792</v>
+        <v>15279652746</v>
       </c>
     </row>
     <row r="532">
       <c r="A532" t="n">
-        <v>15279090178</v>
+        <v>15281416970</v>
       </c>
     </row>
     <row r="533">
       <c r="A533" t="n">
-        <v>15280123397</v>
+        <v>15280871680</v>
       </c>
     </row>
     <row r="534">
       <c r="A534" t="n">
-        <v>15273659894</v>
+        <v>15282618082</v>
       </c>
     </row>
     <row r="535">
       <c r="A535" t="n">
-        <v>15280695022</v>
+        <v>15273020853</v>
       </c>
     </row>
     <row r="536">
       <c r="A536" t="n">
-        <v>15284969607</v>
+        <v>15280500955</v>
       </c>
     </row>
     <row r="537">
       <c r="A537" t="n">
-        <v>15272001943</v>
+        <v>15280500263</v>
       </c>
     </row>
     <row r="538">
       <c r="A538" t="n">
-        <v>15278774814</v>
+        <v>15280739039</v>
       </c>
     </row>
     <row r="539">
       <c r="A539" t="n">
-        <v>15270441478</v>
+        <v>15273703025</v>
       </c>
     </row>
     <row r="540">
       <c r="A540" t="n">
-        <v>15276848617</v>
+        <v>15283883534</v>
       </c>
     </row>
     <row r="541">
       <c r="A541" t="n">
-        <v>15279852808</v>
+        <v>15262845544</v>
       </c>
     </row>
     <row r="542">
       <c r="A542" t="n">
-        <v>15282733803</v>
+        <v>15282430996</v>
       </c>
     </row>
     <row r="543">
       <c r="A543" t="n">
-        <v>15277616869</v>
+        <v>15283731155</v>
       </c>
     </row>
     <row r="544">
       <c r="A544" t="n">
-        <v>15275035878</v>
+        <v>15278419157</v>
       </c>
     </row>
     <row r="545">
       <c r="A545" t="n">
-        <v>15274547969</v>
+        <v>15282267900</v>
       </c>
     </row>
     <row r="546">
       <c r="A546" t="n">
-        <v>15277874196</v>
+        <v>15281873029</v>
       </c>
     </row>
     <row r="547">
       <c r="A547" t="n">
-        <v>15270840531</v>
+        <v>15279484646</v>
       </c>
     </row>
     <row r="548">
       <c r="A548" t="n">
-        <v>15277678714</v>
+        <v>15282403666</v>
       </c>
     </row>
     <row r="549">
       <c r="A549" t="n">
-        <v>15282403881</v>
+        <v>15282246295</v>
       </c>
     </row>
     <row r="550">
       <c r="A550" t="n">
-        <v>15280072640</v>
+        <v>15278280730</v>
       </c>
     </row>
     <row r="551">
       <c r="A551" t="n">
-        <v>15283355934</v>
+        <v>15285125622</v>
       </c>
     </row>
     <row r="552">
       <c r="A552" t="n">
-        <v>15278206190</v>
+        <v>15280766702</v>
       </c>
     </row>
     <row r="553">
       <c r="A553" t="n">
-        <v>15272948091</v>
+        <v>15278672078</v>
       </c>
     </row>
     <row r="554">
       <c r="A554" t="n">
-        <v>15273877106</v>
+        <v>15283355940</v>
       </c>
     </row>
     <row r="555">
       <c r="A555" t="n">
-        <v>15274988193</v>
+        <v>15276255517</v>
       </c>
     </row>
     <row r="556">
       <c r="A556" t="n">
-        <v>15276330921</v>
+        <v>15280641491</v>
       </c>
     </row>
     <row r="557">
       <c r="A557" t="n">
-        <v>15281414677</v>
+        <v>15275036735</v>
       </c>
     </row>
     <row r="558">
       <c r="A558" t="n">
-        <v>15280350456</v>
+        <v>15273488527</v>
       </c>
     </row>
     <row r="559">
       <c r="A559" t="n">
-        <v>15281190198</v>
+        <v>15280112762</v>
       </c>
     </row>
     <row r="560">
       <c r="A560" t="n">
-        <v>15276084154</v>
+        <v>15269650228</v>
       </c>
     </row>
     <row r="561">
       <c r="A561" t="n">
-        <v>15270938006</v>
+        <v>15282730302</v>
       </c>
     </row>
     <row r="562">
       <c r="A562" t="n">
-        <v>15280641491</v>
+        <v>15283224721</v>
       </c>
     </row>
     <row r="563">
       <c r="A563" t="n">
-        <v>15275247304</v>
+        <v>15284969607</v>
       </c>
     </row>
     <row r="564">
       <c r="A564" t="n">
-        <v>15279716510</v>
+        <v>15279196672</v>
       </c>
     </row>
     <row r="565">
       <c r="A565" t="n">
-        <v>15280500263</v>
+        <v>15276671584</v>
       </c>
     </row>
     <row r="566">
       <c r="A566" t="n">
-        <v>15281335502</v>
+        <v>15279249224</v>
       </c>
     </row>
     <row r="567">
       <c r="A567" t="n">
-        <v>15272387464</v>
+        <v>15283230832</v>
       </c>
     </row>
     <row r="568">
       <c r="A568" t="n">
-        <v>15281018961</v>
+        <v>15278759126</v>
       </c>
     </row>
     <row r="569">
       <c r="A569" t="n">
-        <v>15278904343</v>
+        <v>15271053273</v>
       </c>
     </row>
     <row r="570">
       <c r="A570" t="n">
-        <v>15284454092</v>
+        <v>15280592997</v>
       </c>
     </row>
     <row r="571">
       <c r="A571" t="n">
-        <v>15271002528</v>
+        <v>15273888072</v>
       </c>
     </row>
     <row r="572">
       <c r="A572" t="n">
-        <v>15283342415</v>
+        <v>15284110340</v>
       </c>
     </row>
     <row r="573">
       <c r="A573" t="n">
-        <v>15270831378</v>
+        <v>15269786513</v>
       </c>
     </row>
     <row r="574">
       <c r="A574" t="n">
-        <v>15280872112</v>
+        <v>15282245237</v>
       </c>
     </row>
     <row r="575">
       <c r="A575" t="n">
-        <v>15280779151</v>
+        <v>15280184912</v>
       </c>
     </row>
     <row r="576">
       <c r="A576" t="n">
-        <v>15280355553</v>
+        <v>15270769946</v>
       </c>
     </row>
     <row r="577">
       <c r="A577" t="n">
-        <v>15280766702</v>
+        <v>15280732951</v>
       </c>
     </row>
     <row r="578">
       <c r="A578" t="n">
-        <v>15277860727</v>
+        <v>15279681361</v>
       </c>
     </row>
     <row r="579">
       <c r="A579" t="n">
-        <v>15280450769</v>
+        <v>15266967144</v>
       </c>
     </row>
     <row r="580">
       <c r="A580" t="n">
-        <v>15278548206</v>
+        <v>15280406218</v>
       </c>
     </row>
     <row r="581">
       <c r="A581" t="n">
-        <v>15273640584</v>
+        <v>15282686790</v>
       </c>
     </row>
     <row r="582">
       <c r="A582" t="n">
-        <v>15281184068</v>
+        <v>15270465844</v>
       </c>
     </row>
     <row r="583">
       <c r="A583" t="n">
-        <v>15269190347</v>
+        <v>15272522309</v>
       </c>
     </row>
     <row r="584">
       <c r="A584" t="n">
-        <v>15272522309</v>
+        <v>15281879492</v>
       </c>
     </row>
     <row r="585">
       <c r="A585" t="n">
-        <v>15283982021</v>
+        <v>15276830486</v>
       </c>
     </row>
     <row r="586">
       <c r="A586" t="n">
-        <v>15273275714</v>
+        <v>15272384469</v>
       </c>
     </row>
     <row r="587">
       <c r="A587" t="n">
-        <v>15272193128</v>
+        <v>15275705449</v>
       </c>
     </row>
     <row r="588">
       <c r="A588" t="n">
-        <v>15282618082</v>
+        <v>15280562891</v>
       </c>
     </row>
     <row r="589">
       <c r="A589" t="n">
-        <v>15280882333</v>
+        <v>15283982021</v>
       </c>
     </row>
     <row r="590">
       <c r="A590" t="n">
-        <v>15282202569</v>
+        <v>15278946510</v>
       </c>
     </row>
     <row r="591">
       <c r="A591" t="n">
-        <v>15275071001</v>
+        <v>15277139099</v>
       </c>
     </row>
     <row r="592">
       <c r="A592" t="n">
-        <v>15278837726</v>
+        <v>15282684710</v>
       </c>
     </row>
     <row r="593">
       <c r="A593" t="n">
-        <v>15271352219</v>
+        <v>15270360466</v>
       </c>
     </row>
     <row r="594">
       <c r="A594" t="n">
-        <v>15278335488</v>
+        <v>15280777498</v>
       </c>
     </row>
     <row r="595">
       <c r="A595" t="n">
-        <v>15275272586</v>
+        <v>15283723505</v>
       </c>
     </row>
     <row r="596">
       <c r="A596" t="n">
-        <v>15280269880</v>
+        <v>15277914432</v>
       </c>
     </row>
     <row r="597">
       <c r="A597" t="n">
-        <v>15282684710</v>
+        <v>15279702626</v>
       </c>
     </row>
     <row r="598">
       <c r="A598" t="n">
-        <v>15275785410</v>
+        <v>15281080714</v>
       </c>
     </row>
     <row r="599">
       <c r="A599" t="n">
-        <v>15271219238</v>
+        <v>15279680226</v>
       </c>
     </row>
     <row r="600">
       <c r="A600" t="n">
-        <v>15281763755</v>
+        <v>15283342415</v>
       </c>
     </row>
     <row r="601">
       <c r="A601" t="n">
-        <v>15282501599</v>
+        <v>15274890236</v>
       </c>
     </row>
     <row r="602">
       <c r="A602" t="n">
-        <v>15273672743</v>
+        <v>15278096296</v>
       </c>
     </row>
     <row r="603">
       <c r="A603" t="n">
-        <v>15276769498</v>
+        <v>15274412649</v>
       </c>
     </row>
     <row r="604">
       <c r="A604" t="n">
-        <v>15280739022</v>
+        <v>15273667050</v>
       </c>
     </row>
     <row r="605">
       <c r="A605" t="n">
-        <v>15276519638</v>
+        <v>15280956679</v>
       </c>
     </row>
     <row r="606">
       <c r="A606" t="n">
-        <v>15278819786</v>
+        <v>15273699941</v>
       </c>
     </row>
     <row r="607">
       <c r="A607" t="n">
-        <v>15283236834</v>
+        <v>15275281476</v>
       </c>
     </row>
     <row r="608">
       <c r="A608" t="n">
-        <v>15270551083</v>
+        <v>15279770983</v>
       </c>
     </row>
     <row r="609">
       <c r="A609" t="n">
-        <v>15280811723</v>
+        <v>15278157816</v>
       </c>
     </row>
     <row r="610">
       <c r="A610" t="n">
-        <v>15279305686</v>
+        <v>15272850253</v>
       </c>
     </row>
     <row r="611">
       <c r="A611" t="n">
-        <v>15269207070</v>
+        <v>15280602033</v>
       </c>
     </row>
     <row r="612">
       <c r="A612" t="n">
-        <v>586508604</v>
+        <v>15282268098</v>
       </c>
     </row>
     <row r="613">
       <c r="A613" t="n">
-        <v>15281024636</v>
+        <v>15277069756</v>
       </c>
     </row>
     <row r="614">
       <c r="A614" t="n">
-        <v>15280689543</v>
+        <v>15279479439</v>
       </c>
     </row>
     <row r="615">
       <c r="A615" t="n">
-        <v>15280773912</v>
+        <v>15275705450</v>
       </c>
     </row>
     <row r="616">
       <c r="A616" t="n">
-        <v>15271408231</v>
+        <v>15280695022</v>
       </c>
     </row>
     <row r="617">
       <c r="A617" t="n">
-        <v>15265641778</v>
+        <v>15279648741</v>
       </c>
     </row>
     <row r="618">
       <c r="A618" t="n">
-        <v>15271453437</v>
+        <v>15280882333</v>
       </c>
     </row>
     <row r="619">
       <c r="A619" t="n">
-        <v>15274739297</v>
+        <v>15268143667</v>
       </c>
     </row>
     <row r="620">
       <c r="A620" t="n">
-        <v>15280237193</v>
+        <v>15274327709</v>
       </c>
     </row>
     <row r="621">
       <c r="A621" t="n">
-        <v>15280192197</v>
+        <v>15278172609</v>
       </c>
     </row>
     <row r="622">
       <c r="A622" t="n">
-        <v>15279313348</v>
+        <v>15279372315</v>
       </c>
     </row>
     <row r="623">
       <c r="A623" t="n">
-        <v>15273501191</v>
+        <v>15275902197</v>
       </c>
     </row>
     <row r="624">
       <c r="A624" t="n">
-        <v>15280777498</v>
+        <v>15268169332</v>
       </c>
     </row>
     <row r="625">
       <c r="A625" t="n">
-        <v>15281424218</v>
+        <v>15279744659</v>
       </c>
     </row>
     <row r="626">
       <c r="A626" t="n">
-        <v>15277698537</v>
+        <v>15278451924</v>
       </c>
     </row>
     <row r="627">
       <c r="A627" t="n">
-        <v>15281315534</v>
+        <v>15277296786</v>
       </c>
     </row>
     <row r="628">
       <c r="A628" t="n">
-        <v>15281759820</v>
+        <v>15278548206</v>
       </c>
     </row>
     <row r="629">
       <c r="A629" t="n">
-        <v>15281164468</v>
+        <v>15281633615</v>
       </c>
     </row>
     <row r="630">
       <c r="A630" t="n">
-        <v>15275247282</v>
+        <v>15279744514</v>
       </c>
     </row>
     <row r="631">
       <c r="A631" t="n">
-        <v>15280502882</v>
+        <v>15281646010</v>
       </c>
     </row>
     <row r="632">
       <c r="A632" t="n">
-        <v>15279314061</v>
+        <v>15280367828</v>
       </c>
     </row>
     <row r="633">
       <c r="A633" t="n">
-        <v>15274327709</v>
+        <v>15273509085</v>
       </c>
     </row>
     <row r="634">
       <c r="A634" t="n">
-        <v>15281414442</v>
+        <v>15280465256</v>
       </c>
     </row>
     <row r="635">
       <c r="A635" t="n">
-        <v>15279702146</v>
+        <v>15271408231</v>
       </c>
     </row>
     <row r="636">
       <c r="A636" t="n">
-        <v>15282148182</v>
+        <v>15273276079</v>
       </c>
     </row>
     <row r="637">
       <c r="A637" t="n">
-        <v>15280728971</v>
+        <v>15270141908</v>
       </c>
     </row>
     <row r="638">
       <c r="A638" t="n">
-        <v>15272097850</v>
+        <v>15284006716</v>
       </c>
     </row>
     <row r="639">
       <c r="A639" t="n">
-        <v>15276088223</v>
+        <v>15278699629</v>
       </c>
     </row>
     <row r="640">
       <c r="A640" t="n">
-        <v>15269429301</v>
+        <v>15279235255</v>
       </c>
     </row>
     <row r="641">
       <c r="A641" t="n">
-        <v>15276428457</v>
+        <v>15279484648</v>
       </c>
     </row>
     <row r="642">
       <c r="A642" t="n">
-        <v>15274746994</v>
+        <v>15278837726</v>
       </c>
     </row>
     <row r="643">
       <c r="A643" t="n">
-        <v>15267898117</v>
+        <v>15272781600</v>
       </c>
     </row>
     <row r="644">
       <c r="A644" t="n">
-        <v>15281228787</v>
+        <v>15276835424</v>
       </c>
     </row>
     <row r="645">
       <c r="A645" t="n">
-        <v>15281351909</v>
+        <v>15277078618</v>
       </c>
     </row>
     <row r="646">
       <c r="A646" t="n">
-        <v>15276117881</v>
+        <v>15281235151</v>
       </c>
     </row>
     <row r="647">
       <c r="A647" t="n">
-        <v>15269859448</v>
+        <v>15274877104</v>
       </c>
     </row>
     <row r="648">
       <c r="A648" t="n">
-        <v>15277078618</v>
+        <v>15278478047</v>
       </c>
     </row>
     <row r="649">
       <c r="A649" t="n">
-        <v>15269127403</v>
+        <v>15274824201</v>
       </c>
     </row>
     <row r="650">
       <c r="A650" t="n">
-        <v>15278908990</v>
+        <v>15279366507</v>
       </c>
     </row>
     <row r="651">
       <c r="A651" t="n">
-        <v>15269949238</v>
+        <v>15280889466</v>
       </c>
     </row>
     <row r="652">
       <c r="A652" t="n">
-        <v>15262845544</v>
+        <v>15279252082</v>
       </c>
     </row>
     <row r="653">
       <c r="A653" t="n">
-        <v>15283042231</v>
+        <v>15283454557</v>
       </c>
     </row>
     <row r="654">
       <c r="A654" t="n">
-        <v>15281367321</v>
+        <v>15276424116</v>
       </c>
     </row>
     <row r="655">
       <c r="A655" t="n">
-        <v>15279854927</v>
+        <v>15275328011</v>
       </c>
     </row>
     <row r="656">
       <c r="A656" t="n">
-        <v>15273488527</v>
+        <v>15271989345</v>
       </c>
     </row>
     <row r="657">
       <c r="A657" t="n">
-        <v>15274890283</v>
+        <v>15268929026</v>
       </c>
     </row>
     <row r="658">
       <c r="A658" t="n">
-        <v>15269786539</v>
+        <v>15279249351</v>
       </c>
     </row>
     <row r="659">
       <c r="A659" t="n">
-        <v>15280402311</v>
+        <v>15282597869</v>
       </c>
     </row>
     <row r="660">
       <c r="A660" t="n">
-        <v>15274250218</v>
+        <v>15280974033</v>
       </c>
     </row>
     <row r="661">
       <c r="A661" t="n">
-        <v>15279000913</v>
+        <v>15280959003</v>
       </c>
     </row>
     <row r="662">
       <c r="A662" t="n">
-        <v>15281057790</v>
+        <v>15273275714</v>
       </c>
     </row>
     <row r="663">
       <c r="A663" t="n">
-        <v>15270465844</v>
+        <v>15269949061</v>
       </c>
     </row>
     <row r="664">
       <c r="A664" t="n">
-        <v>15282384290</v>
+        <v>15279630161</v>
       </c>
     </row>
     <row r="665">
       <c r="A665" t="n">
-        <v>15282339837</v>
+        <v>15281339674</v>
       </c>
     </row>
     <row r="666">
       <c r="A666" t="n">
-        <v>586498865</v>
+        <v>15282325597</v>
       </c>
     </row>
     <row r="667">
       <c r="A667" t="n">
-        <v>15280703365</v>
+        <v>15279260033</v>
       </c>
     </row>
     <row r="668">
       <c r="A668" t="n">
-        <v>15281317392</v>
+        <v>15281315534</v>
       </c>
     </row>
     <row r="669">
       <c r="A669" t="n">
-        <v>15282395666</v>
+        <v>15279138984</v>
       </c>
     </row>
     <row r="670">
       <c r="A670" t="n">
-        <v>15278774920</v>
+        <v>15279744015</v>
       </c>
     </row>
     <row r="671">
       <c r="A671" t="n">
-        <v>15278546547</v>
+        <v>15281406342</v>
       </c>
     </row>
     <row r="672">
       <c r="A672" t="n">
-        <v>15280406218</v>
+        <v>15280733098</v>
       </c>
     </row>
     <row r="673">
       <c r="A673" t="n">
-        <v>15279379522</v>
+        <v>15280562892</v>
       </c>
     </row>
     <row r="674">
       <c r="A674" t="n">
-        <v>15280499145</v>
+        <v>15273672743</v>
       </c>
     </row>
     <row r="675">
       <c r="A675" t="n">
-        <v>15280885745</v>
+        <v>15282743297</v>
       </c>
     </row>
     <row r="676">
       <c r="A676" t="n">
-        <v>15272781600</v>
+        <v>15276464257</v>
       </c>
     </row>
     <row r="677">
       <c r="A677" t="n">
-        <v>15278358483</v>
+        <v>15278452069</v>
       </c>
     </row>
     <row r="678">
       <c r="A678" t="n">
-        <v>15282051753</v>
+        <v>15282311576</v>
       </c>
     </row>
     <row r="679">
       <c r="A679" t="n">
-        <v>15282335222</v>
+        <v>15277804412</v>
       </c>
     </row>
     <row r="680">
       <c r="A680" t="n">
-        <v>15280726633</v>
+        <v>15277079397</v>
       </c>
     </row>
     <row r="681">
       <c r="A681" t="n">
-        <v>15271527819</v>
+        <v>15270941674</v>
       </c>
     </row>
     <row r="682">
       <c r="A682" t="n">
-        <v>15280367828</v>
+        <v>15278769866</v>
       </c>
     </row>
     <row r="683">
       <c r="A683" t="n">
-        <v>15281214504</v>
+        <v>15280403344</v>
       </c>
     </row>
     <row r="684">
       <c r="A684" t="n">
-        <v>15283224721</v>
+        <v>15281291706</v>
       </c>
     </row>
     <row r="685">
       <c r="A685" t="n">
-        <v>15281070924</v>
+        <v>15279090178</v>
       </c>
     </row>
     <row r="686">
       <c r="A686" t="n">
-        <v>15281667468</v>
+        <v>15275650204</v>
       </c>
     </row>
     <row r="687">
       <c r="A687" t="n">
-        <v>15271703038</v>
+        <v>15280672553</v>
       </c>
     </row>
     <row r="688">
       <c r="A688" t="n">
-        <v>15279761132</v>
+        <v>15282561502</v>
       </c>
     </row>
     <row r="689">
       <c r="A689" t="n">
-        <v>15278646969</v>
+        <v>15275247282</v>
       </c>
     </row>
     <row r="690">
       <c r="A690" t="n">
-        <v>15283341665</v>
+        <v>15270464085</v>
       </c>
     </row>
     <row r="691">
       <c r="A691" t="n">
-        <v>15281413587</v>
+        <v>15269705348</v>
       </c>
     </row>
     <row r="692">
       <c r="A692" t="n">
-        <v>15279003659</v>
+        <v>15273704188</v>
       </c>
     </row>
     <row r="693">
       <c r="A693" t="n">
-        <v>15280637573</v>
+        <v>15277174179</v>
       </c>
     </row>
     <row r="694">
       <c r="A694" t="n">
-        <v>15270929195</v>
+        <v>15276464255</v>
       </c>
     </row>
     <row r="695">
       <c r="A695" t="n">
-        <v>15270652901</v>
+        <v>15282390126</v>
       </c>
     </row>
     <row r="696">
       <c r="A696" t="n">
-        <v>15277069756</v>
+        <v>15282430709</v>
       </c>
     </row>
     <row r="697">
       <c r="A697" t="n">
-        <v>15278144830</v>
+        <v>15281277602</v>
       </c>
     </row>
     <row r="698">
       <c r="A698" t="n">
-        <v>15282672704</v>
+        <v>15276624514</v>
       </c>
     </row>
     <row r="699">
       <c r="A699" t="n">
-        <v>15282500664</v>
+        <v>15274746994</v>
       </c>
     </row>
     <row r="700">
       <c r="A700" t="n">
-        <v>15279422207</v>
+        <v>15281370834</v>
       </c>
     </row>
     <row r="701">
       <c r="A701" t="n">
-        <v>15284006716</v>
+        <v>15279852808</v>
       </c>
     </row>
     <row r="702">
       <c r="A702" t="n">
-        <v>15279744015</v>
+        <v>15281763755</v>
       </c>
     </row>
     <row r="703">
       <c r="A703" t="n">
-        <v>15280612258</v>
+        <v>15282471994</v>
       </c>
     </row>
     <row r="704">
       <c r="A704" t="n">
-        <v>15278893879</v>
+        <v>15275314240</v>
       </c>
     </row>
     <row r="705">
       <c r="A705" t="n">
-        <v>15277945157</v>
+        <v>15277077778</v>
       </c>
     </row>
     <row r="706">
       <c r="A706" t="n">
-        <v>15280239585</v>
+        <v>15280465197</v>
       </c>
     </row>
     <row r="707">
       <c r="A707" t="n">
-        <v>15280724860</v>
+        <v>15284454092</v>
       </c>
     </row>
     <row r="708">
       <c r="A708" t="n">
-        <v>15281234189</v>
+        <v>15281589569</v>
       </c>
     </row>
     <row r="709">
       <c r="A709" t="n">
-        <v>15281333876</v>
+        <v>15284496037</v>
       </c>
     </row>
     <row r="710">
       <c r="A710" t="n">
-        <v>15270111470</v>
+        <v>15274824142</v>
       </c>
     </row>
     <row r="711">
       <c r="A711" t="n">
-        <v>15280553889</v>
+        <v>15276624803</v>
       </c>
     </row>
     <row r="712">
       <c r="A712" t="n">
-        <v>15283454557</v>
+        <v>15271350668</v>
       </c>
     </row>
     <row r="713">
       <c r="A713" t="n">
-        <v>15272725121</v>
+        <v>15280773912</v>
       </c>
     </row>
     <row r="714">
       <c r="A714" t="n">
-        <v>15281411799</v>
+        <v>15281057790</v>
       </c>
     </row>
     <row r="715">
       <c r="A715" t="n">
-        <v>15274450986</v>
+        <v>15281235778</v>
       </c>
     </row>
     <row r="716">
       <c r="A716" t="n">
-        <v>15273488519</v>
+        <v>15271087770</v>
       </c>
     </row>
     <row r="717">
       <c r="A717" t="n">
-        <v>15282268519</v>
+        <v>15278347937</v>
       </c>
     </row>
     <row r="718">
       <c r="A718" t="n">
-        <v>15280769876</v>
+        <v>15279681336</v>
       </c>
     </row>
     <row r="719">
       <c r="A719" t="n">
-        <v>15282852697</v>
+        <v>15275247319</v>
       </c>
     </row>
     <row r="720">
       <c r="A720" t="n">
-        <v>15282966257</v>
+        <v>15282285273</v>
       </c>
     </row>
     <row r="721">
       <c r="A721" t="n">
-        <v>15280592997</v>
+        <v>15280072640</v>
       </c>
     </row>
     <row r="722">
       <c r="A722" t="n">
-        <v>15278672078</v>
+        <v>15280764731</v>
       </c>
     </row>
     <row r="723">
       <c r="A723" t="n">
-        <v>15280465256</v>
+        <v>15279707698</v>
       </c>
     </row>
     <row r="724">
       <c r="A724" t="n">
-        <v>15281336121</v>
+        <v>15283236834</v>
       </c>
     </row>
     <row r="725">
       <c r="A725" t="n">
-        <v>15275606489</v>
+        <v>15279138699</v>
       </c>
     </row>
     <row r="726">
       <c r="A726" t="n">
-        <v>15282533862</v>
+        <v>15273987341</v>
       </c>
     </row>
     <row r="727">
       <c r="A727" t="n">
-        <v>15269741791</v>
+        <v>15274970831</v>
       </c>
     </row>
     <row r="728">
       <c r="A728" t="n">
-        <v>15282334932</v>
+        <v>15278707472</v>
       </c>
     </row>
     <row r="729">
       <c r="A729" t="n">
-        <v>15278144625</v>
+        <v>15283103312</v>
       </c>
     </row>
     <row r="730">
       <c r="A730" t="n">
-        <v>15276464255</v>
+        <v>15281291696</v>
       </c>
     </row>
     <row r="731">
       <c r="A731" t="n">
-        <v>15278494558</v>
+        <v>15278878662</v>
       </c>
     </row>
     <row r="732">
       <c r="A732" t="n">
-        <v>203823276</v>
+        <v>15276136426</v>
       </c>
     </row>
     <row r="733">
       <c r="A733" t="n">
-        <v>15279260033</v>
+        <v>15272033704</v>
       </c>
     </row>
     <row r="734">
       <c r="A734" t="n">
-        <v>15275260003</v>
+        <v>15277616885</v>
       </c>
     </row>
     <row r="735">
       <c r="A735" t="n">
-        <v>15271923861</v>
+        <v>15276088246</v>
       </c>
     </row>
     <row r="736">
       <c r="A736" t="n">
-        <v>15274888692</v>
+        <v>15279900144</v>
       </c>
     </row>
     <row r="737">
       <c r="A737" t="n">
-        <v>15274767088</v>
+        <v>15280129574</v>
       </c>
     </row>
     <row r="738">
       <c r="A738" t="n">
-        <v>15280594997</v>
+        <v>15273285991</v>
       </c>
     </row>
     <row r="739">
       <c r="A739" t="n">
-        <v>15272680107</v>
+        <v>15279773259</v>
       </c>
     </row>
     <row r="740">
       <c r="A740" t="n">
-        <v>15280881791</v>
+        <v>15282179133</v>
       </c>
     </row>
     <row r="741">
       <c r="A741" t="n">
-        <v>15283096155</v>
+        <v>15278207824</v>
       </c>
     </row>
     <row r="742">
       <c r="A742" t="n">
-        <v>15282322025</v>
+        <v>15274888692</v>
       </c>
     </row>
     <row r="743">
       <c r="A743" t="n">
-        <v>587149917</v>
+        <v>15276830184</v>
       </c>
     </row>
     <row r="744">
       <c r="A744" t="n">
-        <v>15282179133</v>
+        <v>15280922608</v>
       </c>
     </row>
     <row r="745">
       <c r="A745" t="n">
-        <v>15281445850</v>
+        <v>15276424037</v>
       </c>
     </row>
     <row r="746">
       <c r="A746" t="n">
-        <v>15278451907</v>
+        <v>15281318940</v>
       </c>
     </row>
     <row r="747">
       <c r="A747" t="n">
-        <v>15281590903</v>
+        <v>15281335757</v>
       </c>
     </row>
     <row r="748">
       <c r="A748" t="n">
-        <v>15285125622</v>
+        <v>15269934045</v>
       </c>
     </row>
     <row r="749">
       <c r="A749" t="n">
-        <v>15271411674</v>
+        <v>15274988193</v>
       </c>
     </row>
     <row r="750">
       <c r="A750" t="n">
-        <v>15277654978</v>
+        <v>15279305686</v>
       </c>
     </row>
     <row r="751">
       <c r="A751" t="n">
-        <v>15282325597</v>
+        <v>15274250218</v>
       </c>
     </row>
     <row r="752">
       <c r="A752" t="n">
-        <v>15269934045</v>
+        <v>15270237795</v>
       </c>
     </row>
     <row r="753">
       <c r="A753" t="n">
-        <v>15281195411</v>
+        <v>15280703365</v>
       </c>
     </row>
     <row r="754">
       <c r="A754" t="n">
-        <v>15273667050</v>
+        <v>15282278094</v>
       </c>
     </row>
     <row r="755">
       <c r="A755" t="n">
-        <v>15281516303</v>
+        <v>15280824014</v>
       </c>
     </row>
     <row r="756">
       <c r="A756" t="n">
-        <v>15281818722</v>
+        <v>15278530436</v>
       </c>
     </row>
     <row r="757">
       <c r="A757" t="n">
-        <v>15279955789</v>
+        <v>15276848617</v>
       </c>
     </row>
     <row r="758">
       <c r="A758" t="n">
-        <v>15270812613</v>
+        <v>15281317392</v>
       </c>
     </row>
     <row r="759">
       <c r="A759" t="n">
-        <v>15277101734</v>
+        <v>15270551083</v>
       </c>
     </row>
     <row r="760">
       <c r="A760" t="n">
-        <v>15275882167</v>
+        <v>15283278326</v>
       </c>
     </row>
     <row r="761">
       <c r="A761" t="n">
-        <v>15279138699</v>
+        <v>15279168595</v>
       </c>
     </row>
     <row r="762">
       <c r="A762" t="n">
-        <v>15279090280</v>
+        <v>15278967698</v>
       </c>
     </row>
     <row r="763">
       <c r="A763" t="n">
-        <v>15275036735</v>
+        <v>15276519639</v>
       </c>
     </row>
     <row r="764">
       <c r="A764" t="n">
-        <v>15280073374</v>
+        <v>15283903910</v>
       </c>
     </row>
     <row r="765">
       <c r="A765" t="n">
-        <v>15271938620</v>
+        <v>15280811723</v>
       </c>
     </row>
     <row r="766">
       <c r="A766" t="n">
-        <v>15276519639</v>
+        <v>15279365654</v>
       </c>
     </row>
     <row r="767">
       <c r="A767" t="n">
-        <v>15282378677</v>
+        <v>15281333876</v>
       </c>
     </row>
     <row r="768">
       <c r="A768" t="n">
-        <v>15270737568</v>
+        <v>15278517314</v>
       </c>
     </row>
     <row r="769">
       <c r="A769" t="n">
-        <v>15279681336</v>
+        <v>15268192994</v>
       </c>
     </row>
     <row r="770">
       <c r="A770" t="n">
-        <v>15280978307</v>
+        <v>15282471976</v>
       </c>
     </row>
     <row r="771">
       <c r="A771" t="n">
-        <v>15281335757</v>
+        <v>15282856978</v>
       </c>
     </row>
     <row r="772">
       <c r="A772" t="n">
-        <v>15281224320</v>
+        <v>15280587105</v>
       </c>
     </row>
     <row r="773">
       <c r="A773" t="n">
-        <v>15280701337</v>
+        <v>15283721361</v>
       </c>
     </row>
     <row r="774">
       <c r="A774" t="n">
-        <v>15273638582</v>
+        <v>15281414442</v>
       </c>
     </row>
     <row r="775">
       <c r="A775" t="n">
-        <v>15281903756</v>
+        <v>15280729737</v>
       </c>
     </row>
     <row r="776">
       <c r="A776" t="n">
-        <v>15278452069</v>
+        <v>15273564998</v>
       </c>
     </row>
     <row r="777">
       <c r="A777" t="n">
-        <v>15281330161</v>
+        <v>15278892986</v>
       </c>
     </row>
     <row r="778">
       <c r="A778" t="n">
-        <v>15283858331</v>
+        <v>15269741791</v>
       </c>
     </row>
     <row r="779">
       <c r="A779" t="n">
-        <v>15273667031</v>
+        <v>15278206190</v>
       </c>
     </row>
     <row r="780">
       <c r="A780" t="n">
-        <v>15281666842</v>
+        <v>15271448058</v>
       </c>
     </row>
     <row r="781">
       <c r="A781" t="n">
-        <v>15269226775</v>
+        <v>15276088223</v>
       </c>
     </row>
     <row r="782">
       <c r="A782" t="n">
-        <v>15275247319</v>
+        <v>15280192197</v>
       </c>
     </row>
     <row r="783">
       <c r="A783" t="n">
-        <v>15278280730</v>
+        <v>15282268519</v>
       </c>
     </row>
     <row r="784">
       <c r="A784" t="n">
-        <v>15280729737</v>
+        <v>15278819786</v>
       </c>
     </row>
     <row r="785">
       <c r="A785" t="n">
-        <v>15274984701</v>
+        <v>15276769498</v>
       </c>
     </row>
     <row r="786">
       <c r="A786" t="n">
-        <v>15272552656</v>
+        <v>15279003659</v>
       </c>
     </row>
     <row r="787">
       <c r="A787" t="n">
-        <v>15273704188</v>
+        <v>15271525049</v>
       </c>
     </row>
     <row r="788">
       <c r="A788" t="n">
-        <v>15280274289</v>
+        <v>15280872112</v>
       </c>
     </row>
     <row r="789">
       <c r="A789" t="n">
-        <v>15278419157</v>
+        <v>15279090322</v>
       </c>
     </row>
     <row r="790">
       <c r="A790" t="n">
-        <v>15269428857</v>
+        <v>15279422172</v>
       </c>
     </row>
     <row r="791">
       <c r="A791" t="n">
-        <v>15274824142</v>
+        <v>15281628958</v>
       </c>
     </row>
     <row r="792">
       <c r="A792" t="n">
-        <v>15280355547</v>
+        <v>15282734582</v>
       </c>
     </row>
     <row r="793">
       <c r="A793" t="n">
-        <v>15277239776</v>
+        <v>15269429301</v>
       </c>
     </row>
     <row r="794">
       <c r="A794" t="n">
-        <v>15276424116</v>
+        <v>15282538492</v>
       </c>
     </row>
     <row r="795">
       <c r="A795" t="n">
-        <v>15277945198</v>
+        <v>15275035878</v>
       </c>
     </row>
     <row r="796">
       <c r="A796" t="n">
-        <v>15275544645</v>
+        <v>15280238394</v>
       </c>
     </row>
     <row r="797">
       <c r="A797" t="n">
-        <v>15271023824</v>
+        <v>15273275702</v>
       </c>
     </row>
     <row r="798">
       <c r="A798" t="n">
-        <v>15280361201</v>
+        <v>15281190008</v>
       </c>
     </row>
     <row r="799">
       <c r="A799" t="n">
-        <v>15283096154</v>
+        <v>15283334869</v>
       </c>
     </row>
     <row r="800">
       <c r="A800" t="n">
-        <v>15280738479</v>
+        <v>15281759820</v>
       </c>
     </row>
     <row r="801">
       <c r="A801" t="n">
-        <v>15283355940</v>
+        <v>15279681035</v>
       </c>
     </row>
     <row r="802">
       <c r="A802" t="n">
-        <v>15280562892</v>
+        <v>15280822869</v>
       </c>
     </row>
     <row r="803">
       <c r="A803" t="n">
-        <v>15283100226</v>
+        <v>15282386548</v>
       </c>
     </row>
     <row r="804">
       <c r="A804" t="n">
-        <v>15277945167</v>
+        <v>15280239585</v>
       </c>
     </row>
     <row r="805">
       <c r="A805" t="n">
-        <v>15272549283</v>
+        <v>15283042231</v>
       </c>
     </row>
     <row r="806">
       <c r="A806" t="n">
-        <v>15283343393</v>
+        <v>15280738459</v>
       </c>
     </row>
     <row r="807">
       <c r="A807" t="n">
-        <v>15278290271</v>
+        <v>15284454314</v>
       </c>
     </row>
     <row r="808">
       <c r="A808" t="n">
-        <v>15275545818</v>
+        <v>15272776383</v>
       </c>
     </row>
     <row r="809">
       <c r="A809" t="n">
-        <v>15279422172</v>
+        <v>15280612258</v>
       </c>
     </row>
     <row r="810">
       <c r="A810" t="n">
-        <v>15276769808</v>
+        <v>15283858331</v>
       </c>
     </row>
     <row r="811">
       <c r="A811" t="n">
-        <v>15282301419</v>
+        <v>15269764221</v>
       </c>
     </row>
     <row r="812">
       <c r="A812" t="n">
-        <v>15280737284</v>
+        <v>15279422137</v>
       </c>
     </row>
     <row r="813">
       <c r="A813" t="n">
-        <v>15273888402</v>
+        <v>15281228787</v>
       </c>
     </row>
     <row r="814">
       <c r="A814" t="n">
-        <v>15268559158</v>
+        <v>15279356900</v>
       </c>
     </row>
     <row r="815">
       <c r="A815" t="n">
-        <v>15278759126</v>
+        <v>15278144625</v>
       </c>
     </row>
     <row r="816">
       <c r="A816" t="n">
-        <v>15279061766</v>
+        <v>15273877106</v>
       </c>
     </row>
     <row r="817">
       <c r="A817" t="n">
-        <v>15268558674</v>
+        <v>15278290271</v>
       </c>
     </row>
     <row r="818">
       <c r="A818" t="n">
-        <v>15279565932</v>
+        <v>15282460769</v>
       </c>
     </row>
     <row r="819">
       <c r="A819" t="n">
-        <v>15280601971</v>
+        <v>15278872569</v>
       </c>
     </row>
     <row r="820">
       <c r="A820" t="n">
-        <v>15281531506</v>
+        <v>15278967933</v>
       </c>
     </row>
     <row r="821">
       <c r="A821" t="n">
-        <v>15273731880</v>
+        <v>15282403881</v>
       </c>
     </row>
     <row r="822">
       <c r="A822" t="n">
-        <v>15282471874</v>
+        <v>15281674909</v>
       </c>
     </row>
     <row r="823">
       <c r="A823" t="n">
-        <v>15278898659</v>
+        <v>15273659894</v>
       </c>
     </row>
     <row r="824">
       <c r="A824" t="n">
-        <v>15280815542</v>
+        <v>15277913805</v>
       </c>
     </row>
     <row r="825">
-      <c r="A825" t="n">
-        <v>15271122455</v>
+      <c r="A825" t="inlineStr">
+        <is>
+          <t>587149917</t>
+        </is>
       </c>
     </row>
     <row r="826">
-      <c r="A826" t="n">
-        <v>15280980028</v>
+      <c r="A826" t="inlineStr">
+        <is>
+          <t>586836203</t>
+        </is>
       </c>
     </row>
     <row r="827">
-      <c r="A827" t="n">
-        <v>15270464165</v>
+      <c r="A827" t="inlineStr">
+        <is>
+          <t>203832841</t>
+        </is>
       </c>
     </row>
     <row r="828">
-      <c r="A828" t="n">
-        <v>15282386580</v>
+      <c r="A828" t="inlineStr">
+        <is>
+          <t>586450613</t>
+        </is>
       </c>
     </row>
     <row r="829">
-      <c r="A829" t="n">
-        <v>15273266760</v>
+      <c r="A829" t="inlineStr">
+        <is>
+          <t>203760504</t>
+        </is>
       </c>
     </row>
     <row r="830">
       <c r="A830" t="inlineStr">
         <is>
-          <t>587240796</t>
+          <t>586669159</t>
         </is>
       </c>
     </row>
     <row r="831">
       <c r="A831" t="inlineStr">
         <is>
-          <t>15268236400</t>
+          <t>203753716</t>
         </is>
       </c>
     </row>
     <row r="832">
       <c r="A832" t="inlineStr">
         <is>
-          <t>203800063</t>
+          <t>203806239</t>
         </is>
       </c>
     </row>
     <row r="833">
       <c r="A833" t="inlineStr">
         <is>
-          <t>586669159</t>
+          <t>586508604</t>
         </is>
       </c>
     </row>
     <row r="834">
       <c r="A834" t="inlineStr">
         <is>
-          <t>586731172</t>
+          <t>587038733</t>
         </is>
       </c>
     </row>
     <row r="835">
       <c r="A835" t="inlineStr">
         <is>
-          <t>586450613</t>
+          <t>587019784</t>
         </is>
       </c>
     </row>
     <row r="836">
       <c r="A836" t="inlineStr">
         <is>
-          <t>587272994</t>
+          <t>586498865</t>
         </is>
       </c>
     </row>
     <row r="837">
       <c r="A837" t="inlineStr">
         <is>
-          <t>587019784</t>
+          <t>587272994</t>
         </is>
       </c>
     </row>
     <row r="838">
       <c r="A838" t="inlineStr">
         <is>
-          <t>587064055</t>
+          <t>587077298</t>
         </is>
       </c>
     </row>
     <row r="839">
       <c r="A839" t="inlineStr">
         <is>
-          <t>203837249</t>
+          <t>587064055</t>
         </is>
       </c>
     </row>
     <row r="840">
       <c r="A840" t="inlineStr">
         <is>
-          <t>586836203</t>
+          <t>587053093</t>
         </is>
       </c>
     </row>
     <row r="841">
       <c r="A841" t="inlineStr">
         <is>
-          <t>15268215653</t>
+          <t>586456182</t>
         </is>
       </c>
     </row>
     <row r="842">
       <c r="A842" t="inlineStr">
         <is>
-          <t>203753716</t>
+          <t>203845090</t>
         </is>
       </c>
     </row>
     <row r="843">
       <c r="A843" t="inlineStr">
         <is>
-          <t>203806239</t>
+          <t>203190018</t>
         </is>
       </c>
     </row>
     <row r="844">
       <c r="A844" t="inlineStr">
         <is>
-          <t>586456182</t>
+          <t>203777260</t>
         </is>
       </c>
     </row>
     <row r="845">
       <c r="A845" t="inlineStr">
         <is>
-          <t>203832841</t>
+          <t>586731172</t>
         </is>
       </c>
     </row>
     <row r="846">
       <c r="A846" t="inlineStr">
         <is>
-          <t>15276769595</t>
+          <t>203837249</t>
         </is>
       </c>
     </row>
     <row r="847">
       <c r="A847" t="inlineStr">
         <is>
-          <t>203845090</t>
+          <t>203823276</t>
         </is>
       </c>
     </row>
     <row r="848">
       <c r="A848" t="inlineStr">
         <is>
-          <t>203777260</t>
+          <t>587240796</t>
         </is>
       </c>
     </row>
     <row r="849">
       <c r="A849" t="inlineStr">
         <is>
-          <t>587077298</t>
+          <t>586514541</t>
         </is>
       </c>
     </row>
     <row r="850">
       <c r="A850" t="inlineStr">
         <is>
-          <t>203190018</t>
-        </is>
-      </c>
-    </row>
-    <row r="851">
-      <c r="A851" t="inlineStr">
-        <is>
-          <t>203760504</t>
+          <t>203800063</t>
         </is>
       </c>
     </row>
